--- a/src/main/resources/espacios/2 Step/0 - Phrasal Verb.xlsx
+++ b/src/main/resources/espacios/2 Step/0 - Phrasal Verb.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="1 Phrasal Verb" sheetId="1" state="visible" r:id="rId3"/>
@@ -1828,6 +1828,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1898,7 +1899,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2030,7 +2031,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D43"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.2"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="2" style="1" width="11.53"/>
@@ -2569,7 +2570,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D46"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.71"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="2" style="1" width="11.53"/>
@@ -3144,10 +3145,11 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D43"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.42"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="2" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="3" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3683,12 +3685,12 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D77"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.41"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="31.75"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="4" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="30.6"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
